--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -91,34 +91,34 @@
     <t>mongodb://localhost:27017/</t>
   </si>
   <si>
-    <t>MJBeta1</t>
-  </si>
-  <si>
-    <t>MJBeta2</t>
-  </si>
-  <si>
-    <t>MJBeta3</t>
-  </si>
-  <si>
-    <t>MJBeta1000(center)</t>
+    <t>LDBeta1</t>
+  </si>
+  <si>
+    <t>LDBeta2</t>
+  </si>
+  <si>
+    <t>LDBeta3</t>
+  </si>
+  <si>
+    <t>LDBeta1000(center)</t>
   </si>
   <si>
     <t>#中心服</t>
   </si>
   <si>
-    <t>MJBeta1001(robot)</t>
+    <t>LDBeta1001(robot)</t>
   </si>
   <si>
     <t>#机器人</t>
   </si>
   <si>
-    <t>MJBeta1002(router)</t>
+    <t>LDBeta1002(router)</t>
   </si>
   <si>
     <t>路由区</t>
   </si>
   <si>
-    <t>MJBeta1011</t>
+    <t>LDBeta1011</t>
   </si>
   <si>
     <t>版号区</t>
@@ -300,12 +300,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1142,7 +1142,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" spans="3:7">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="3:6">
+    <row r="4" spans="3:7">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" spans="3:7">
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:6">
+    <row r="6" s="1" customFormat="1" spans="3:7">
       <c r="C6" s="5">
         <v>1</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="3:6">
+    <row r="7" s="1" customFormat="1" spans="3:7">
       <c r="C7" s="5">
         <v>2</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="3:6">
+    <row r="8" spans="3:7">
       <c r="C8" s="3">
         <v>3</v>
       </c>
